--- a/artfynd/A 27635-2025 artfynd.xlsx
+++ b/artfynd/A 27635-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017084</v>
       </c>
       <c r="B2" t="n">
-        <v>91212</v>
+        <v>91216</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27635-2025 artfynd.xlsx
+++ b/artfynd/A 27635-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017084</v>
       </c>
       <c r="B2" t="n">
-        <v>91216</v>
+        <v>91218</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27635-2025 artfynd.xlsx
+++ b/artfynd/A 27635-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017084</v>
       </c>
       <c r="B2" t="n">
-        <v>91218</v>
+        <v>91220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27635-2025 artfynd.xlsx
+++ b/artfynd/A 27635-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017084</v>
       </c>
       <c r="B2" t="n">
-        <v>91220</v>
+        <v>91222</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27635-2025 artfynd.xlsx
+++ b/artfynd/A 27635-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017084</v>
       </c>
       <c r="B2" t="n">
-        <v>91222</v>
+        <v>91226</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27635-2025 artfynd.xlsx
+++ b/artfynd/A 27635-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017084</v>
       </c>
       <c r="B2" t="n">
-        <v>91226</v>
+        <v>91229</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
